--- a/Trabalho M2/OUTPUT_3.4_CBR_vs_RN/Common/Comparacao_CBR_vs_RN.xlsx
+++ b/Trabalho M2/OUTPUT_3.4_CBR_vs_RN/Common/Comparacao_CBR_vs_RN.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="40" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="60" uniqueCount="21">
   <si>
     <t>metodo</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t>RN classifica com base no modelo aprendido durante o treino.</t>
+  </si>
+  <si>
+    <t>Topologia: 14 | Treino: trainlm | Saida: logsig</t>
   </si>
 </sst>
 </file>
@@ -197,7 +200,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F3" s="0">
         <v>100</v>
